--- a/analysis/tables/TinyLlama-1.1B-intermediate-step-480k-1T.xlsx
+++ b/analysis/tables/TinyLlama-1.1B-intermediate-step-480k-1T.xlsx
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4239497787480961</v>
+        <v>0.4241088223917047</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.002565950749334717</v>
+        <v>-0.002672392594289641</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -506,19 +506,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6409382230977771</v>
+        <v>0.6412372970886957</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07803030766595925</v>
+        <v>0.07802020755710587</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006052487530272687</v>
+        <v>0.006301195479073135</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4213838279987614</v>
+        <v>0.4214364297974151</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1349180652311648</v>
+        <v>0.1349073854191462</v>
       </c>
     </row>
     <row r="3">
@@ -536,30 +536,30 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6571883236464123</v>
+        <v>0.5610932385381719</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.07570714552882743</v>
+        <v>-0.07300308705943037</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.657x - 0.076</t>
+          <t>y = 0.561x - 0.073</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7604217987621019</v>
+        <v>0.76182750160554</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07134529350853232</v>
+        <v>0.07081018425509757</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1151985554289309</v>
+        <v>0.1301086558263059</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5814811781175849</v>
+        <v>0.4880901514787416</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1349180652311648</v>
+        <v>0.1349073854191462</v>
       </c>
     </row>
     <row r="4">
@@ -577,30 +577,30 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7474851936761759</v>
+        <v>0.5594533277307201</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01832184813714574</v>
+        <v>-0.06745494153047216</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.747x + 0.018</t>
+          <t>y = 0.559x - 0.067</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8387172441999282</v>
+        <v>0.7669477731529121</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06886641041966188</v>
+        <v>0.0706474762101917</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02451131914337703</v>
+        <v>0.1205729561107196</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7658070418133217</v>
+        <v>0.4919983862002479</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1349180652311648</v>
+        <v>0.1349073854191462</v>
       </c>
     </row>
   </sheetData>
